--- a/artfynd/A 32178-2022 artfynd.xlsx
+++ b/artfynd/A 32178-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32178-2022 artfynd.xlsx
+++ b/artfynd/A 32178-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6418503</v>
+        <v>271504</v>
       </c>
       <c r="B2" t="n">
-        <v>103251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224098</v>
+        <v>872</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skäftekärr väst, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620514.2219599612</v>
+        <v>620430</v>
       </c>
       <c r="R2" t="n">
-        <v>6347123.560176011</v>
+        <v>6347101</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +752,9 @@
           <t>2008-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,63 +782,53 @@
           <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1051054</v>
+        <v>272042</v>
       </c>
       <c r="B3" t="n">
-        <v>88855</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>872</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skäftekärr väst, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620486.2208894386</v>
+        <v>620439</v>
       </c>
       <c r="R3" t="n">
-        <v>6347135.188476902</v>
+        <v>6347119</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +858,9 @@
           <t>2010-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,69 +885,66 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1691473</v>
+        <v>58537739</v>
       </c>
       <c r="B4" t="n">
-        <v>88852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>872</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skäftekärr väst, Öl</t>
+          <t>Skäftekärr, Böda Kronopark, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620486.2208894386</v>
+        <v>620503</v>
       </c>
       <c r="R4" t="n">
-        <v>6347135.188476902</v>
+        <v>6347138</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2016-04-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2016-04-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,83 +994,82 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog med barrförna</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Stefan Cherrug</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Stefan Cherrug</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1691472</v>
+        <v>68946490</v>
       </c>
       <c r="B5" t="n">
-        <v>88852</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4189</v>
+        <v>872</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skäftekärr väst, Öl</t>
+          <t>Skäftekärr NV-ut, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620648.4060886779</v>
+        <v>620441</v>
       </c>
       <c r="R5" t="n">
-        <v>6347005.165690679</v>
+        <v>6347120</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2017-11-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2017-11-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tre ex, upp till 4 meter höga. Rikligt med bär.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,33 +1127,32 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>barrskog med barrförna</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Håkan Lundkvist, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Joakim Ekman, Gabriel Ekman, Björn Owe-Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>272042</v>
+        <v>78379407</v>
       </c>
       <c r="B6" t="n">
-        <v>104625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,19 +1178,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skäftekärr väst, Öl</t>
+          <t>Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620438.9788100726</v>
+        <v>620569</v>
       </c>
       <c r="R6" t="n">
-        <v>6347118.647305055</v>
+        <v>6347037</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,22 +1218,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,76 +1232,87 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrskog med barrförna</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Håkan Lernefalk, Niklas Hjort, Ulrika Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6418523</v>
+        <v>132180752</v>
       </c>
       <c r="B7" t="n">
-        <v>103251</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107771</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224098</v>
+        <v>872</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skäftekärr väst, Öl</t>
+          <t>Skäfteskärr, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620521.8242545642</v>
+        <v>620426</v>
       </c>
       <c r="R7" t="n">
-        <v>6347123.241896702</v>
+        <v>6347116</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,22 +1336,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,85 +1350,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>barrskog med barrförna</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Krister Wahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+          <t>Krister Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6419147</v>
+        <v>947644</v>
       </c>
       <c r="B8" t="n">
-        <v>103252</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224098</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäftekärr, Öl</t>
+          <t>Skäftekärr väst, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620497.9520432136</v>
+        <v>620421</v>
       </c>
       <c r="R8" t="n">
-        <v>6347142.027941524</v>
+        <v>6347059</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,27 +1434,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>bland införda barrträd</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,71 +1453,75 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>stigkant i barrskog</t>
+          <t>barrskog med barrförna</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Svenson, Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1691545</v>
+        <v>1051054</v>
       </c>
       <c r="B9" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4189</v>
+        <v>2008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skäftekärr NV, Öl</t>
+          <t>Skäftekärr väst, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620454.5088434923</v>
+        <v>620486</v>
       </c>
       <c r="R9" t="n">
-        <v>6347162.405297283</v>
+        <v>6347135</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,22 +1545,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,18 +1564,18 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>barrskog med barrförna</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1655,12 +1585,7 @@
         <v>1053274</v>
       </c>
       <c r="B10" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1607,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1701,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620589.6193752112</v>
+        <v>620590</v>
       </c>
       <c r="R10" t="n">
-        <v>6347086.258384107</v>
+        <v>6347086</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1734,19 +1659,9 @@
           <t>2012-11-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-11-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1783,37 +1698,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78379403</v>
+        <v>1691472</v>
       </c>
       <c r="B11" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>4189</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1821,23 +1731,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skäftekärr, Öl</t>
+          <t>Skäftekärr väst, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620569.3720610167</v>
+        <v>620648</v>
       </c>
       <c r="R11" t="n">
-        <v>6347036.947578875</v>
+        <v>6347005</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,22 +1772,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,73 +1788,78 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>barrskog med barrförna</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk, Niklas Hjort, Ulrika Lernefalk</t>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Håkan Lundkvist, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78379473</v>
+        <v>1691473</v>
       </c>
       <c r="B12" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223246</v>
+        <v>4189</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skäftekärr, Öl</t>
+          <t>Skäftekärr väst, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620569.3720610167</v>
+        <v>620486</v>
       </c>
       <c r="R12" t="n">
-        <v>6347036.947578875</v>
+        <v>6347135</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1977,22 +1883,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,76 +1897,71 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>barrskog med barrförna</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk, Niklas Hjort, Ulrika Lernefalk</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>78379407</v>
+        <v>1691545</v>
       </c>
       <c r="B13" t="n">
-        <v>104626</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>872</v>
+        <v>4189</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnek</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skäftekärr, Öl</t>
+          <t>Skäftekärr NV, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620569.3720610167</v>
+        <v>620455</v>
       </c>
       <c r="R13" t="n">
-        <v>6347036.947578875</v>
+        <v>6347162</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,22 +1985,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,86 +1999,79 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk, Niklas Hjort, Ulrika Lernefalk</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68946490</v>
+        <v>78379403</v>
       </c>
       <c r="B14" t="n">
-        <v>104626</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>872</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järnek</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skäftekärr NV-ut, Öl</t>
+          <t>Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620441.0988002012</v>
+        <v>620569</v>
       </c>
       <c r="R14" t="n">
-        <v>6347120.333312213</v>
+        <v>6347037</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2221,27 +2095,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-11-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-11-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tre ex, upp till 4 meter höga. Rikligt med bär.</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,58 +2111,48 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Björn Owe-Larsson</t>
+          <t>Håkan Lernefalk, Niklas Hjort, Ulrika Lernefalk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>58537739</v>
+        <v>58537834</v>
       </c>
       <c r="B15" t="n">
-        <v>104626</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>872</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järnek</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2311,19 +2160,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skäftekärr, Böda Kronopark, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620502.9400496923</v>
+        <v>620503</v>
       </c>
       <c r="R15" t="n">
-        <v>6347138.385250439</v>
+        <v>6347138</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2389,6 +2238,868 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2921189</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skäftekärr väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>620651</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6346955</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2306850</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skäftekärr väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>620635</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6346956</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2008-05-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2008-05-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>blandskog/vägkant</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5745313</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skäftekärr väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>620635</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6346956</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2008-05-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2008-05-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>blandskog/vägkant</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>78379473</v>
+      </c>
+      <c r="B19" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620569</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6347037</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-05-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-05-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk, Niklas Hjort, Ulrika Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6418503</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skäftekärr väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>620514</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6347124</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6418523</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skäftekärr väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>620522</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6347123</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>barrskog med barrförna</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6418524</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skäftekärr väst, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>620540</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6346978</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Jan-Olof Petersson, Ingrid Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6419147</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>620498</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6347142</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2011-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2011-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>bland införda barrträd</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>stigkant i barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32178-2022 artfynd.xlsx
+++ b/artfynd/A 32178-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/271504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/272042</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58537739</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68946490</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1277,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78379407</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132180752</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/947644</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1051054</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1053274</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1691472</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1691473</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,6 +2079,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1691545</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78379403</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2238,6 +2308,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58537834</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2344,6 +2419,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2921189</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2450,6 +2530,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2306850</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,6 +2639,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5745313</t>
         </is>
       </c>
     </row>
@@ -2662,6 +2752,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78379473</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,6 +2863,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6418503</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2874,6 +2974,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6418523</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2980,6 +3085,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6418524</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3100,8 +3210,37 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6419147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>